--- a/Mundial 2026/mundial2026_panini - Baca.xlsx
+++ b/Mundial 2026/mundial2026_panini - Baca.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuari\Documents\Cromos\Mundial 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F380DCF1-8881-40FC-9570-4732C7AA5DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F92FB7-F0EF-487B-87DA-3B4609C0470A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="45" activeTab="48" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -6610,11 +6610,8 @@
     <xf numFmtId="0" fontId="3" fillId="64" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6679,6 +6676,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -7064,7 +7064,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="33"/>
@@ -7202,11 +7202,11 @@
       </c>
       <c r="F6" s="7">
         <f>SUM('GRUPO A · Korea Republic'!F3:F22)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="8">
         <f>SUM('GRUPO A · Korea Republic'!G3:G22)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -7426,11 +7426,11 @@
       </c>
       <c r="F14" s="7">
         <f>SUM('GRUPO C · Haiti'!F3:F22)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14" s="8">
         <f>SUM('GRUPO C · Haiti'!G3:G22)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -7454,11 +7454,11 @@
       </c>
       <c r="F15" s="7">
         <f>SUM('GRUPO C · Scotland'!F3:F22)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G15" s="8">
         <f>SUM('GRUPO C · Scotland'!G3:G22)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -7510,11 +7510,11 @@
       </c>
       <c r="F17" s="7">
         <f>SUM('GRUPO D · Paraguay'!F3:F22)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" s="8">
         <f>SUM('GRUPO D · Paraguay'!G3:G22)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -7818,11 +7818,11 @@
       </c>
       <c r="F28" s="7">
         <f>SUM('GRUPO G · Belgium'!F3:F22)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" s="8">
         <f>SUM('GRUPO G · Belgium'!G3:G22)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -8434,11 +8434,11 @@
       </c>
       <c r="F50" s="7">
         <f>SUM('GRUPO L · Ghana'!F3:F22)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G50" s="8">
         <f>SUM('GRUPO L · Ghana'!G3:G22)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -8575,15 +8575,15 @@
       </c>
       <c r="F55" s="16">
         <f t="shared" si="0"/>
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="G55" s="17">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="34" t="s">
+      <c r="A57" s="32" t="s">
         <v>61</v>
       </c>
       <c r="B57" s="33"/>
@@ -8616,7 +8616,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="33"/>
@@ -9071,7 +9071,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="43" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="33"/>
@@ -9526,7 +9526,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="33"/>
@@ -9958,7 +9958,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="45" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="33"/>
@@ -10278,11 +10278,11 @@
         <v>2</v>
       </c>
       <c r="F17" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -10409,7 +10409,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="46" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="33"/>
@@ -10659,11 +10659,11 @@
         <v>2</v>
       </c>
       <c r="F14" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -10840,7 +10840,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="47" t="s">
         <v>21</v>
       </c>
       <c r="B1" s="33"/>
@@ -11281,7 +11281,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="48" t="s">
         <v>22</v>
       </c>
       <c r="B1" s="33"/>
@@ -11445,11 +11445,11 @@
         <v>3</v>
       </c>
       <c r="F9" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -11712,7 +11712,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>23</v>
       </c>
       <c r="B1" s="33"/>
@@ -12159,7 +12159,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>24</v>
       </c>
       <c r="B1" s="33"/>
@@ -12602,7 +12602,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="51" t="s">
         <v>25</v>
       </c>
       <c r="B1" s="33"/>
@@ -13067,7 +13067,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="33"/>
@@ -13304,7 +13304,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="46" t="s">
         <v>26</v>
       </c>
       <c r="B1" s="33"/>
@@ -13755,7 +13755,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="52" t="s">
         <v>767</v>
       </c>
       <c r="B1" s="33"/>
@@ -14222,7 +14222,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="53" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="33"/>
@@ -14673,7 +14673,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="54" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="33"/>
@@ -15126,7 +15126,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="55" t="s">
         <v>30</v>
       </c>
       <c r="B1" s="33"/>
@@ -15585,7 +15585,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="56" t="s">
         <v>31</v>
       </c>
       <c r="B1" s="33"/>
@@ -16531,11 +16531,11 @@
         <v>3</v>
       </c>
       <c r="F3" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="24">
         <f t="shared" ref="G3:G22" si="0">MAX(0,IF(E3="",0,E3)-IF(F3="",0,F3))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -17812,7 +17812,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="36" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="33"/>
@@ -18251,7 +18251,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="51" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="33"/>
@@ -20448,7 +20448,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="41" t="s">
         <v>41</v>
       </c>
       <c r="B1" s="33"/>
@@ -22655,7 +22655,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="37" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="33"/>
@@ -26714,7 +26714,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>54</v>
       </c>
       <c r="B1" s="33"/>
@@ -27340,10 +27340,12 @@
       <c r="E9" s="22">
         <v>1</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="23">
+        <v>1</v>
+      </c>
       <c r="G9" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -27622,7 +27624,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="33"/>
@@ -27916,11 +27918,11 @@
         <v>7</v>
       </c>
       <c r="F16" s="23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="24">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -29423,7 +29425,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="33"/>
@@ -29862,7 +29864,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="33"/>
@@ -30309,7 +30311,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="41" t="s">
         <v>14</v>
       </c>
       <c r="B1" s="33"/>
@@ -30760,7 +30762,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="42" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="33"/>

--- a/Mundial 2026/mundial2026_panini - Baca.xlsx
+++ b/Mundial 2026/mundial2026_panini - Baca.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Cromos\Mundial 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8763732E-53AC-469F-97D2-05E1E99C02CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7ED71C-908E-40C3-8B6A-C2CE1232AF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="18" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="48" activeTab="49" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -6610,7 +6610,7 @@
     <xf numFmtId="0" fontId="3" fillId="64" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="55" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -6664,9 +6664,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6736,6 +6733,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="54" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="55" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="56" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -7202,11 +7202,11 @@
       </c>
       <c r="F6" s="7">
         <f>SUM('GRUPO A · Korea Republic'!F3:F22)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="8">
         <f>SUM('GRUPO A · Korea Republic'!G3:G22)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -7398,11 +7398,11 @@
       </c>
       <c r="F13" s="7">
         <f>SUM('GRUPO C · Morocco'!F3:F22)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G13" s="8">
         <f>SUM('GRUPO C · Morocco'!G3:G22)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -7482,11 +7482,11 @@
       </c>
       <c r="F16" s="7">
         <f>SUM('GRUPO D · USA'!F3:F22)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="8">
         <f>SUM('GRUPO D · USA'!G3:G22)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -8462,11 +8462,11 @@
       </c>
       <c r="F51" s="7">
         <f>SUM('GRUPO L · Panamá'!F3:F22)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G51" s="8">
         <f>SUM('GRUPO L · Panamá'!G3:G22)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -8575,11 +8575,11 @@
       </c>
       <c r="F55" s="16">
         <f t="shared" si="0"/>
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G55" s="17">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -9574,11 +9574,11 @@
         <v>2</v>
       </c>
       <c r="F3" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="24">
         <f t="shared" ref="G3:G22" si="0">MAX(0,IF(E3="",0,E3)-IF(F3="",0,F3))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -11094,11 +11094,11 @@
         <v>3</v>
       </c>
       <c r="F14" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="24">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -12604,7 +12604,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="32" t="s">
         <v>25</v>
       </c>
       <c r="B1" s="33"/>
@@ -13759,7 +13759,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="52" t="s">
         <v>767</v>
       </c>
       <c r="B1" s="33"/>
@@ -14226,7 +14226,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="53" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="33"/>
@@ -14677,7 +14677,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="54" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="33"/>
@@ -15130,7 +15130,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="55" t="s">
         <v>30</v>
       </c>
       <c r="B1" s="33"/>
@@ -15589,7 +15589,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="56" t="s">
         <v>31</v>
       </c>
       <c r="B1" s="33"/>
@@ -16044,7 +16044,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="33"/>
@@ -16487,7 +16487,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="58" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="33"/>
@@ -16922,7 +16922,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="59" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="33"/>
@@ -17361,7 +17361,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="60" t="s">
         <v>35</v>
       </c>
       <c r="B1" s="33"/>
@@ -18255,7 +18255,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="33"/>
@@ -18698,7 +18698,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="61" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="33"/>
@@ -19121,7 +19121,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="62" t="s">
         <v>38</v>
       </c>
       <c r="B1" s="33"/>
@@ -19584,7 +19584,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="63" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="33"/>
@@ -20017,7 +20017,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="64" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="33"/>
@@ -20887,7 +20887,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="65" t="s">
         <v>42</v>
       </c>
       <c r="B1" s="33"/>
@@ -21330,7 +21330,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="66" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="33"/>
@@ -21785,7 +21785,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="67" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="33"/>
@@ -22212,7 +22212,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="64" t="s">
         <v>45</v>
       </c>
       <c r="B1" s="33"/>
@@ -23106,7 +23106,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="68" t="s">
         <v>46</v>
       </c>
       <c r="B1" s="33"/>
@@ -23565,7 +23565,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="69" t="s">
         <v>47</v>
       </c>
       <c r="B1" s="33"/>
@@ -24024,7 +24024,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="66" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="33"/>
@@ -24471,7 +24471,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>49</v>
       </c>
       <c r="B1" s="33"/>
@@ -24918,7 +24918,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="71" t="s">
         <v>50</v>
       </c>
       <c r="B1" s="33"/>
@@ -25381,7 +25381,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>51</v>
       </c>
       <c r="B1" s="33"/>
@@ -25840,7 +25840,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="73" t="s">
         <v>52</v>
       </c>
       <c r="B1" s="33"/>
@@ -26279,7 +26279,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="74" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="33"/>
@@ -27173,7 +27173,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="75" t="s">
         <v>55</v>
       </c>
       <c r="B1" s="33"/>
@@ -27922,11 +27922,11 @@
         <v>7</v>
       </c>
       <c r="F16" s="23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -28111,11 +28111,11 @@
         <v>2</v>
       </c>
       <c r="F3" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="24">
         <f t="shared" ref="G3:G22" si="0">MAX(0,IF(E3="",0,E3)-IF(F3="",0,F3))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
